--- a/data/trans_dic/P44D-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P44D-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,97; 76,97</t>
+          <t>15,77; 75,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 33,14</t>
+          <t>4,05; 32,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,96</t>
+          <t>2,53; 15,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,16</t>
+          <t>0,0; 32,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,86; 61,86</t>
+          <t>0,0; 61,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 15,27</t>
+          <t>4,92; 15,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,93; 42,55</t>
+          <t>11,55; 43,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,61; 35,73</t>
+          <t>8,48; 34,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 9,2</t>
+          <t>5,13; 13,12</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,18</t>
+          <t>0,0; 29,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,24; 43,48</t>
+          <t>15,81; 42,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,95; 18,84</t>
+          <t>9,77; 19,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,97; 52,72</t>
+          <t>16,54; 52,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,19</t>
+          <t>0,0; 20,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 11,92</t>
+          <t>5,39; 11,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,76; 32,65</t>
+          <t>10,76; 34,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,55; 29,12</t>
+          <t>11,59; 29,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,35; 13,8</t>
+          <t>8,46; 14,05</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,12</t>
+          <t>0,0; 32,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,6</t>
+          <t>0,0; 15,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 14,31</t>
+          <t>6,41; 13,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,78</t>
+          <t>0,0; 27,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 34,55</t>
+          <t>3,79; 33,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 12,0</t>
+          <t>5,45; 11,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 23,32</t>
+          <t>1,81; 22,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 17,61</t>
+          <t>4,01; 18,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,95; 11,98</t>
+          <t>6,63; 11,7</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,46</t>
+          <t>0,0; 22,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 17,65</t>
+          <t>2,03; 15,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 10,0</t>
+          <t>2,38; 10,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 38,11</t>
+          <t>5,1; 43,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,34</t>
+          <t>0,0; 22,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 7,45</t>
+          <t>1,75; 6,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,25; 25,5</t>
+          <t>4,18; 23,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 14,77</t>
+          <t>2,33; 15,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 7,04</t>
+          <t>2,74; 7,28</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,06; 22,96</t>
+          <t>6,58; 22,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,24; 20,88</t>
+          <t>9,12; 20,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 10,61</t>
+          <t>7,54; 12,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,95; 27,58</t>
+          <t>10,57; 27,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,94; 19,58</t>
+          <t>6,02; 19,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 9,18</t>
+          <t>5,78; 9,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,57; 21,61</t>
+          <t>10,35; 21,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,34; 17,88</t>
+          <t>9,02; 17,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 9,02</t>
+          <t>7,24; 10,04</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>14144</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2264; 10908</t>
+          <t>2235; 10630</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1010; 8876</t>
+          <t>1085; 8587</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 29860</t>
+          <t>2400; 14395</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 6597</t>
+          <t>0; 6697</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>978; 6828</t>
+          <t>0; 6752</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3336; 11001</t>
+          <t>3800; 12268</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4137; 14757</t>
+          <t>4007; 14977</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3257; 13513</t>
+          <t>3207; 13074</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2281; 37293</t>
+          <t>8837; 22607</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24248</t>
+          <t>27089</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12488</t>
+          <t>13966</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>36736</t>
+          <t>41055</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 11478</t>
+          <t>0; 11473</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8161; 21854</t>
+          <t>7949; 21392</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16403; 34515</t>
+          <t>18905; 36952</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5063; 17832</t>
+          <t>5596; 17859</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 7102</t>
+          <t>0; 6772</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8305; 18586</t>
+          <t>9441; 20894</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7142; 23889</t>
+          <t>7874; 25516</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10516; 24396</t>
+          <t>9714; 24894</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28333; 46799</t>
+          <t>31186; 51788</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>16923</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11807</t>
+          <t>12655</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27999</t>
+          <t>29578</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 10515</t>
+          <t>0; 10625</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6994</t>
+          <t>0; 6577</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10423; 23456</t>
+          <t>11399; 24243</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 8939</t>
+          <t>0; 9149</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1085; 9817</t>
+          <t>1077; 9513</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7557; 17174</t>
+          <t>8588; 18494</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1880; 15417</t>
+          <t>1198; 14982</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2105; 12425</t>
+          <t>2830; 12797</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21348; 36770</t>
+          <t>22231; 39218</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>10103</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6208</t>
+          <t>0; 6024</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>735; 6773</t>
+          <t>780; 6110</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2327; 9875</t>
+          <t>2567; 11265</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1095; 8116</t>
+          <t>1086; 9363</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 8365</t>
+          <t>0; 8108</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2237; 8077</t>
+          <t>2106; 8359</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2030; 12178</t>
+          <t>1998; 11006</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1852; 10963</t>
+          <t>1727; 11335</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5829; 14580</t>
+          <t>6235; 16588</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51933</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35281</t>
+          <t>38506</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>87214</t>
+          <t>94879</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7959; 25874</t>
+          <t>7418; 25094</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14556; 32903</t>
+          <t>14371; 32738</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21733; 82658</t>
+          <t>43276; 70065</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11935; 30070</t>
+          <t>11527; 29719</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6460; 21299</t>
+          <t>6545; 21487</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27459; 44017</t>
+          <t>30610; 49095</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23433; 47920</t>
+          <t>22938; 48677</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>24879; 47632</t>
+          <t>24014; 47511</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>45666; 113496</t>
+          <t>79876; 110878</t>
         </is>
       </c>
     </row>
